--- a/ProjectTracking_CineMax.xlsx
+++ b/ProjectTracking_CineMax.xlsx
@@ -1,26 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Functions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Use Case" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet sheetId="1" name="Functions" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Use Case" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Functions!$A$1:$N$37</definedName>
+    <definedName name="_xlnm._FilterDatabase">Functions!$A$1:$N$37</definedName>
   </definedNames>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="334">
   <si>
     <t>Screen/Function</t>
   </si>
@@ -28,25 +26,25 @@
     <t>Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Table_name 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table_name 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table_name 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table_name 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use Cases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Charge</t>
+    <t>Table_name 1</t>
+  </si>
+  <si>
+    <t>Table_name 2</t>
+  </si>
+  <si>
+    <t>Table_name 3</t>
+  </si>
+  <si>
+    <t>Table_name 4</t>
+  </si>
+  <si>
+    <t>Business Process</t>
+  </si>
+  <si>
+    <t>Use Cases</t>
+  </si>
+  <si>
+    <t>In Charge</t>
   </si>
   <si>
     <t>Iteration</t>
@@ -61,10 +59,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes / Updates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branch List</t>
+    <t>Notes / Updates</t>
+  </si>
+  <si>
+    <t>Branch List</t>
   </si>
   <si>
     <t>Screen</t>
@@ -73,16 +71,16 @@
     <t>cinemas</t>
   </si>
   <si>
-    <t xml:space="preserve">Cinema Branch Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View/Search Cinema Branches: As an Admin, I want to view all cinema branches across the chain.</t>
+    <t>Cinema Branch Management</t>
+  </si>
+  <si>
+    <t>View/Search Cinema Branches: As an Admin, I want to view all cinema branches across the chain.</t>
   </si>
   <si>
     <t>Dũng</t>
   </si>
   <si>
-    <t xml:space="preserve">Iteration 1</t>
+    <t>Iteration 1</t>
   </si>
   <si>
     <t>M-04.1</t>
@@ -91,37 +89,31 @@
     <t>BranchAdminServlet</t>
   </si>
   <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Da hoan thien CinemaAdminServlet va cinemas.jsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branch Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Cinema Branches: As an Admin, I want to add, edit, or deactivate cinema branches so that I can oversee the cinema chain.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iteration 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can bo sung form Add/Edit cu the cho rap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screening Room List</t>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Branch Management</t>
+  </si>
+  <si>
+    <t>Manage Cinema Branches: As an Admin, I want to add, edit, or deactivate cinema branches so that I can oversee the cinema chain.</t>
+  </si>
+  <si>
+    <t>Iteration 2</t>
+  </si>
+  <si>
+    <t>To Do</t>
+  </si>
+  <si>
+    <t>Screening Room List</t>
   </si>
   <si>
     <t>screening_rooms</t>
   </si>
   <si>
-    <t xml:space="preserve">Showtime &amp; Room Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Screening Rooms: As an Admin, I want to view all rooms by branch so that I can oversee room capacity.</t>
+    <t>Showtime &amp; Room Management</t>
+  </si>
+  <si>
+    <t>View Screening Rooms: As an Admin, I want to view all rooms by branch so that I can oversee room capacity.</t>
   </si>
   <si>
     <t>M-04.2</t>
@@ -130,19 +122,13 @@
     <t>RoomAdminServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">ScreeningRoomService.getRoomsByCinema &amp; ScreeningRoomDAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screening Room Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Screening Rooms: As an Admin, I want to add/edit rooms and room formats (2D, 3D, IMAX).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khung Service da co, can hoan thien UI form JSP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seat Layout Designer</t>
+    <t>Screening Room Management</t>
+  </si>
+  <si>
+    <t>Manage Screening Rooms: As an Admin, I want to add/edit rooms and room formats (2D, 3D, IMAX).</t>
+  </si>
+  <si>
+    <t>Seat Layout Designer</t>
   </si>
   <si>
     <t>seats</t>
@@ -151,10 +137,10 @@
     <t>seat_types</t>
   </si>
   <si>
-    <t xml:space="preserve">Configure Seat Layout: As an Admin, I want to design seat matrix (A-Z x 1-N) and seat types (Standard, VIP, Couple) for each hall.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iteration 3</t>
+    <t>Configure Seat Layout: As an Admin, I want to design seat matrix (A-Z x 1-N) and seat types (Standard, VIP, Couple) for each hall.</t>
+  </si>
+  <si>
+    <t>Iteration 3</t>
   </si>
   <si>
     <t>M-04.3</t>
@@ -163,25 +149,16 @@
     <t>SeatGridServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">To Do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bang seats, seat_types da san sang trong CSDL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seat Maintenance Toggle</t>
+    <t>Seat Maintenance Toggle</t>
   </si>
   <si>
     <t>maintenance_schedules</t>
   </si>
   <si>
-    <t xml:space="preserve">Toggle Seat Maintenance: As an Admin/Manager, I want to mark broken seats under maintenance to prevent sales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cot seats.status (MAINTENANCE, AVAILABLE) &amp; maintenance_schedules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin Dashboard</t>
+    <t>Toggle Seat Maintenance: As an Admin/Manager, I want to mark broken seats under maintenance to prevent sales.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard</t>
   </si>
   <si>
     <t>bookings</t>
@@ -190,10 +167,10 @@
     <t>payments</t>
   </si>
   <si>
-    <t xml:space="preserve">Dashboard &amp; Reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View System Overview: As an Admin, I want a high-level operational overview across all branches.</t>
+    <t>Dashboard &amp; Reporting</t>
+  </si>
+  <si>
+    <t>View System Overview: As an Admin, I want a high-level operational overview across all branches.</t>
   </si>
   <si>
     <t>M-11</t>
@@ -202,10 +179,7 @@
     <t>AdminDashboardServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Da co AdminDashboardServlet &amp; dashboard.jsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue &amp; Sales Reports</t>
+    <t>Revenue &amp; Sales Reports</t>
   </si>
   <si>
     <t>tickets</t>
@@ -214,7 +188,7 @@
     <t>order_items</t>
   </si>
   <si>
-    <t xml:space="preserve">Generate Revenue Reports: As an Admin, I want to view revenue reports by date, movie, branch and export Excel/PDF.</t>
+    <t>Generate Revenue Reports: As an Admin, I want to view revenue reports by date, movie, branch and export Excel/PDF.</t>
   </si>
   <si>
     <t>M-10.1</t>
@@ -223,43 +197,34 @@
     <t>ReportAdminServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Du lieu bang bookings, payments, order_items da san sang cho aggregation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branch Occupancy Report</t>
+    <t>Branch Occupancy Report</t>
   </si>
   <si>
     <t>showtimes</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitor Hall Occupancy: As a Cinema Manager/Admin, I want to track seat occupancy rates across halls and time slots.</t>
+    <t>Monitor Hall Occupancy: As a Cinema Manager/Admin, I want to track seat occupancy rates across halls and time slots.</t>
   </si>
   <si>
     <t>M-10.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Thong ke ty le lap day ghe theo suat chieu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Settings</t>
+    <t>System Settings</t>
   </si>
   <si>
     <t>system_settings</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage System Parameters: As an Admin, I want to configure global params (holding duration, cleaning buffer 15m).</t>
+    <t>System Administration</t>
+  </si>
+  <si>
+    <t>Manage System Parameters: As an Admin, I want to configure global params (holding duration, cleaning buffer 15m).</t>
   </si>
   <si>
     <t>SettingAdminServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Da co SystemSettingDAO doc CLEANING_BUFFER_MINUTES = 15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User Login</t>
+    <t>User Login</t>
   </si>
   <si>
     <t>users</t>
@@ -268,10 +233,10 @@
     <t>roles</t>
   </si>
   <si>
-    <t xml:space="preserve">Authentication &amp; Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login System: As a user, I want to log in with email and password so that I can access authorized features.</t>
+    <t>Authentication &amp; Account</t>
+  </si>
+  <si>
+    <t>Login System: As a user, I want to log in with email and password so that I can access authorized features.</t>
   </si>
   <si>
     <t>Cường</t>
@@ -283,43 +248,31 @@
     <t>AuthServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Da hoan thien AuthServlet, PasswordUtil (BCrypt), login.jsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User Register</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Register Account: As a guest, I want to register an account with OTP email verification so that I can become a member.</t>
+    <t>User Register</t>
+  </si>
+  <si>
+    <t>Register Account: As a guest, I want to register an account with OTP email verification so that I can become a member.</t>
   </si>
   <si>
     <t>M-01.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Da hoan thien dang ky register.jsp, ma hoa BCrypt, gan role CUSTOMER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User Logout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User Logout: As an authenticated user, I want to log out and invalidate my session securely.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Da hoan thien AuthServlet action /logout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forgot Password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reset Password: As a user, I want to reset my password via a 15-minute token/OTP sent to my email.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cot reset_password_token, reset_token_expires_at da co trong CSDL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Profile: As a Customer, I want to view and edit my personal details, phone number, and avatar.</t>
+    <t>User Logout</t>
+  </si>
+  <si>
+    <t>User Logout: As an authenticated user, I want to log out and invalidate my session securely.</t>
+  </si>
+  <si>
+    <t>Forgot Password</t>
+  </si>
+  <si>
+    <t>Reset Password: As a user, I want to reset my password via a 15-minute token/OTP sent to my email.</t>
+  </si>
+  <si>
+    <t>User Profile</t>
+  </si>
+  <si>
+    <t>Manage Profile: As a Customer, I want to view and edit my personal details, phone number, and avatar.</t>
   </si>
   <si>
     <t>M-01.3</t>
@@ -328,22 +281,16 @@
     <t>ProfileServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Method UserDAO.updateProfile da co, can hoan thien JSP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change Password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change Password: As a logged-in user, I want to change my current password to maintain account security.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Da co UserService.changePassword &amp; UserDAO.updatePassword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin User List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Users: As an Admin, I want to view, search, and filter all accounts across the system.</t>
+    <t>Change Password</t>
+  </si>
+  <si>
+    <t>Change Password: As a logged-in user, I want to change my current password to maintain account security.</t>
+  </si>
+  <si>
+    <t>Admin User List</t>
+  </si>
+  <si>
+    <t>Manage Users: As an Admin, I want to view, search, and filter all accounts across the system.</t>
   </si>
   <si>
     <t>M-01.4</t>
@@ -352,19 +299,13 @@
     <t>UserAdminServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Method UserDAO.findAll, findByRole da co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin User Assignment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assign Role &amp; Branch: As an Admin, I want to assign/transfer staff and managers to cinema branches and lock/unlock accounts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cot users.cinema_id va users.status (ACTIVE, LOCKED)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Page &amp; Browsing</t>
+    <t>Admin User Assignment</t>
+  </si>
+  <si>
+    <t>Assign Role &amp; Branch: As an Admin, I want to assign/transfer staff and managers to cinema branches and lock/unlock accounts.</t>
+  </si>
+  <si>
+    <t>Home Page &amp; Browsing</t>
   </si>
   <si>
     <t>movies</t>
@@ -376,10 +317,10 @@
     <t>movie_genres</t>
   </si>
   <si>
-    <t xml:space="preserve">Home &amp; Movie Browsing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Now Showing &amp; Coming Soon: As a guest, I want to browse movies currently showing and coming soon on homepage.</t>
+    <t>Home &amp; Movie Browsing</t>
+  </si>
+  <si>
+    <t>View Now Showing &amp; Coming Soon: As a guest, I want to browse movies currently showing and coming soon on homepage.</t>
   </si>
   <si>
     <t>Thịnh</t>
@@ -388,34 +329,25 @@
     <t>MovieServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Da hoan thien MovieServlet (/movies), MovieDAO, movies.jsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movie Detail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Movie Details: As a user, I want to view trailer, duration, age rating (T13/T16/T18), and synopsis of a movie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Da hoan thien /movie/detail &amp; movie-detail.jsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movie Search &amp; Filter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search &amp; Filter Movies: As a user, I want to search movies by title and filter by genre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MovieDAO.searchMovies da ho tro keyword va the loai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin Movie List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movie Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Master Catalog: As an Admin, I want to view and search all movies in master catalog with pagination.</t>
+    <t>Movie Detail</t>
+  </si>
+  <si>
+    <t>View Movie Details: As a user, I want to view trailer, duration, age rating (T13/T16/T18), and synopsis of a movie.</t>
+  </si>
+  <si>
+    <t>Movie Search &amp; Filter</t>
+  </si>
+  <si>
+    <t>Search &amp; Filter Movies: As a user, I want to search movies by title and filter by genre.</t>
+  </si>
+  <si>
+    <t>Admin Movie List</t>
+  </si>
+  <si>
+    <t>Movie Management</t>
+  </si>
+  <si>
+    <t>Manage Master Catalog: As an Admin, I want to view and search all movies in master catalog with pagination.</t>
   </si>
   <si>
     <t>M-02.1</t>
@@ -424,49 +356,37 @@
     <t>MovieAdminServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Da co MovieDAO.findAll, can giao dien admin quan ly phim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin Movie CRUD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add / Edit / Archive Movie: As an Admin, I want to create or update movie metadata, poster URL, and duration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Da co MovieDAO.insert, update, delete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Showtime Schedule View</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Showtimes: As a customer, I want to view showtime schedules by movie, date, and cinema branch.</t>
+    <t>Admin Movie CRUD</t>
+  </si>
+  <si>
+    <t>Add / Edit / Archive Movie: As an Admin, I want to create or update movie metadata, poster URL, and duration.</t>
+  </si>
+  <si>
+    <t>Showtime Schedule View</t>
+  </si>
+  <si>
+    <t>View Showtimes: As a customer, I want to view showtime schedules by movie, date, and cinema branch.</t>
   </si>
   <si>
     <t>ShowtimeManagementServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">ShowtimeDAO.findByMovieAndDate &amp; findByCinemaAndDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Showtime Creation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schedule Branch Showtimes: As a Cinema Manager, I want to create showtimes with automatic 15-minute cleaning buffer check.</t>
+    <t>Showtime Creation</t>
+  </si>
+  <si>
+    <t>Schedule Branch Showtimes: As a Cinema Manager, I want to create showtimes with automatic 15-minute cleaning buffer check.</t>
   </si>
   <si>
     <t>M-03.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Da hoan thien ShowtimeServiceImpl.createShowtime, buffer 15p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic Pricing Config</t>
+    <t>Dynamic Pricing Config</t>
   </si>
   <si>
     <t>ticket_pricings</t>
   </si>
   <si>
-    <t xml:space="preserve">Configure Pricing Template: As an Admin/Manager, I want to set base prices by format (2D/3D), time slot, and weekend surcharges.</t>
+    <t>Configure Pricing Template: As an Admin/Manager, I want to set base prices by format (2D/3D), time slot, and weekend surcharges.</t>
   </si>
   <si>
     <t>M-03.2</t>
@@ -475,16 +395,13 @@
     <t>PricingAdminServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">TicketPricingDAO &amp; PricingServiceImpl (Pass Unit Test 100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Movie Review</t>
+    <t>Customer Movie Review</t>
   </si>
   <si>
     <t>reviews</t>
   </si>
   <si>
-    <t xml:space="preserve">Rate &amp; Review Movies: As a Customer, I want to rate 1-5 stars and write a review after watching a movie.</t>
+    <t>Rate &amp; Review Movies: As a Customer, I want to rate 1-5 stars and write a review after watching a movie.</t>
   </si>
   <si>
     <t>M-02.2</t>
@@ -493,31 +410,25 @@
     <t>ReviewServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Bang reviews va Review.java da co, can ReviewDAO &amp; UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin Review Moderation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moderate User Reviews: As an Admin, I want to approve, hide, or delete inappropriate reviews.</t>
+    <t>Admin Review Moderation</t>
+  </si>
+  <si>
+    <t>Moderate User Reviews: As an Admin, I want to approve, hide, or delete inappropriate reviews.</t>
   </si>
   <si>
     <t>ReviewAdminServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Cot reviews.is_approved da co trong CSDL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online Seat Selection</t>
+    <t>Online Seat Selection</t>
   </si>
   <si>
     <t>seat_holdings</t>
   </si>
   <si>
-    <t xml:space="preserve">Booking System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select Seats: As a Customer, I want to choose available seats from the visual hall map with seat type pricing.</t>
+    <t>Booking System</t>
+  </si>
+  <si>
+    <t>Select Seats: As a Customer, I want to choose available seats from the visual hall map with seat type pricing.</t>
   </si>
   <si>
     <t>Linh</t>
@@ -529,16 +440,13 @@
     <t>BookingFlowServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Da hoan thien /booking/checkout &amp; checkout.jsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pessimistic Seat Holding</t>
+    <t>Pessimistic Seat Holding</t>
   </si>
   <si>
     <t>Service</t>
   </si>
   <si>
-    <t xml:space="preserve">Temporarily Lock Seats: As the System, I want to lock selected seats for 5 minutes to prevent double booking.</t>
+    <t>Temporarily Lock Seats: As the System, I want to lock selected seats for 5 minutes to prevent double booking.</t>
   </si>
   <si>
     <t>M-05.3</t>
@@ -547,37 +455,28 @@
     <t>BookingEngineServiceImpl</t>
   </si>
   <si>
-    <t xml:space="preserve">SeatHoldingDAO, Concurrency race-condition test 100% pass!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-Release Expired Holds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Expired Seats: As the System, I want to release holds older than 5 minutes automatically.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SeatHoldingDAO.releaseExpiredHoldings() da viet nhung chua co scheduler/cron goi toi - hien chi tu giai phong khi co nguoi khac giu trung dung ghe do qua MERGE, chua phai tu dong quet dinh ky nhu user story mo ta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online Booking Checkout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm Booking: As a Customer, I want to review booking summary, ticket prices, and F&amp;B combos before payment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Da hoan thien BookingFlowServlet.doPost /booking/checkout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VNPay Payment Gateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External API</t>
+    <t>Auto-Release Expired Holds</t>
+  </si>
+  <si>
+    <t>Release Expired Seats: As the System, I want to release holds older than 5 minutes automatically.</t>
+  </si>
+  <si>
+    <t>Online Booking Checkout</t>
+  </si>
+  <si>
+    <t>Confirm Booking: As a Customer, I want to review booking summary, ticket prices, and F&amp;B combos before payment.</t>
+  </si>
+  <si>
+    <t>VNPay Payment Gateway</t>
+  </si>
+  <si>
+    <t>External API</t>
   </si>
   <si>
     <t>Payment</t>
   </si>
   <si>
-    <t xml:space="preserve">Pay via VNPay: As a Customer, I want to pay online securely via VNPay gateway.</t>
+    <t>Pay via VNPay: As a Customer, I want to pay online securely via VNPay gateway.</t>
   </si>
   <si>
     <t>M-06.1</t>
@@ -586,13 +485,10 @@
     <t>PaymentServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">PaymentDAO &amp; mo hinh payments da san sang, mock SUCCESS cho SWP391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Booking History</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Booking History: As a Customer, I want to view my past and upcoming booking details and e-tickets.</t>
+    <t>Customer Booking History</t>
+  </si>
+  <si>
+    <t>View Booking History &amp; Conditional Cancellation: As a Customer, I want to view my past/upcoming bookings and cancel tickets at least X hours before showtime for automated refund and seat release.</t>
   </si>
   <si>
     <t>M-05.4</t>
@@ -601,34 +497,28 @@
     <t>CustomerBookingServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Can viet them BookingDAO.findByUserId va trang JSP ve cua toi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-Ticket QR Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ticket &amp; Entry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View E-Ticket QR: As a Customer, I want to display my unique barcode/QR code ticket on my phone for gate entry.</t>
+    <t>E-Ticket QR Code</t>
+  </si>
+  <si>
+    <t>Ticket &amp; Entry</t>
+  </si>
+  <si>
+    <t>View E-Ticket QR: As a Customer, I want to display my unique barcode/QR code ticket on my phone for gate entry.</t>
   </si>
   <si>
     <t>M-07.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Ma ve TK-{showtimeId}-{seatId}-{UUID} da sinh tu dong trong TicketDAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS Counter Sales</t>
+    <t>POS Counter Sales</t>
   </si>
   <si>
     <t>fnb_items</t>
   </si>
   <si>
-    <t xml:space="preserve">Staff Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sell Tickets &amp; F&amp;B at Counter: As Cinema Staff, I want a fast POS interface to book tickets and snacks for walk-in customers.</t>
+    <t>Staff Operations</t>
+  </si>
+  <si>
+    <t>Sell Tickets &amp; F&amp;B at Counter: As Cinema Staff, I want a fast POS interface to book tickets, select concession ticket types (Standard/Student/Senior) upon ID check, and add snacks for walk-in customers.</t>
   </si>
   <si>
     <t>Tuyển</t>
@@ -640,13 +530,10 @@
     <t>PosCounterServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Da co PosCounterServlet (/admin/operation/pos) va pos-counter.jsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS Checkout &amp; Cashier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Process Counter Payment: As Cinema Staff, I want to accept cash or VNPay at counter and generate immediate ticket prints.</t>
+    <t>POS Checkout &amp; Cashier</t>
+  </si>
+  <si>
+    <t>Process Counter Payment: As Cinema Staff, I want to accept cash or VNPay at counter and generate immediate ticket prints.</t>
   </si>
   <si>
     <t>M-06.2</t>
@@ -655,31 +542,25 @@
     <t>PosOrderServiceImpl</t>
   </si>
   <si>
-    <t xml:space="preserve">Da hoan thien PosOrderServiceImpl.processCounterCheckout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concession Catalog View</t>
+    <t>Concession Catalog View</t>
   </si>
   <si>
     <t>fnb_categories</t>
   </si>
   <si>
-    <t xml:space="preserve">Concessions / Snacks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Browse F&amp;B Menu: As a customer or staff, I want to view available snacks, popcorn, drinks, and combos with prices.</t>
+    <t>Concessions / Snacks</t>
+  </si>
+  <si>
+    <t>Browse F&amp;B Menu: As a customer or staff, I want to view available snacks, popcorn, drinks, and combos with prices.</t>
   </si>
   <si>
     <t>M-08.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Da co FnBItemDAO.findAllActive()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin F&amp;B Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage F&amp;B Catalog: As an Admin, I want to add, edit, or disable snacks and combos.</t>
+    <t>Admin F&amp;B Management</t>
+  </si>
+  <si>
+    <t>Manage F&amp;B Catalog: As an Admin, I want to add, edit, or disable snacks and combos.</t>
   </si>
   <si>
     <t>M-08.1</t>
@@ -688,28 +569,22 @@
     <t>ConcessionAdminServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Bang fnb_items, fnb_categories da co trong CSDL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branch F&amp;B Inventory</t>
+    <t>Branch F&amp;B Inventory</t>
   </si>
   <si>
     <t>cinema_inventories</t>
   </si>
   <si>
-    <t xml:space="preserve">Manage Branch Stock: As a Cinema Manager, I want to update stock quantity of popcorn and cups per branch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bang cinema_inventories da co trong CSDL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QR Ticket Scanner</t>
+    <t>Manage Branch Stock &amp; Real-time Deduction: As a Cinema Manager/System, I want to manage stock quantity, automatically deduct inventory upon payment, and auto-flag Out of Stock when quantity reaches 0.</t>
+  </si>
+  <si>
+    <t>QR Ticket Scanner</t>
   </si>
   <si>
     <t>ticket_checkin_logs</t>
   </si>
   <si>
-    <t xml:space="preserve">Validate QR Ticket: As Cinema Staff, I want to scan customer QR ticket via webcam/scanner to verify validity.</t>
+    <t>Validate QR Ticket: As Cinema Staff, I want to scan customer QR ticket via webcam/scanner to verify validity.</t>
   </si>
   <si>
     <t>M-07.2</t>
@@ -718,85 +593,49 @@
     <t>ScannerServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Da hoan thien ScannerServlet (/admin/operation/scanner) &amp; scanner.jsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gate Checkin Verification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gate Check-in Verification: As the System, I want to verify hall, showtime, age limit (T18), and mark ticket as USED.</t>
+    <t>Gate Checkin Verification</t>
+  </si>
+  <si>
+    <t>Gate Check-in Verification: As the System, I want to verify hall, showtime, age limit (T18), and mark ticket as USED.</t>
   </si>
   <si>
     <t>CheckinServiceImpl</t>
   </si>
   <si>
-    <t xml:space="preserve">Da hoan thien CheckinServiceImpl &amp; CheckinServiceTest (100% pass)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ticket Reissue / Reprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Look Up &amp; Reprint Ticket: As Cinema Staff, I want to search tickets by phone/code and reprint lost tickets.</t>
+    <t>Ticket Reissue, Cancel &amp; Reprint</t>
+  </si>
+  <si>
+    <t>Reissue, Cancel or Reprint Ticket: As Cinema Staff, I want to search tickets by phone/code, reprint lost tickets, or process authorized ticket cancellation and rollback.</t>
   </si>
   <si>
     <t>TicketReprintServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">Can viet them man hinh tra cuu ve theo SĐT tai quay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Shift &amp; Cash Drawer</t>
-  </si>
-  <si>
-    <t>cash_drawers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Shift Cash Drawer: As Cinema Staff, I want to open shift with starting cash and close shift with ending cash reconciliation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vận hành ca</t>
-  </si>
-  <si>
-    <t>CashDrawerServlet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bang cash_drawers (bang so 31 trong 01_schema.sql) va model CashDrawer.java</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shift Sales Reconciliation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Personal Shift Report: As Cinema Staff, I want to view my cash sales summary at the end of my shift.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bang cash_drawers co total_cash_sales, difference_amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entity1 (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entity2 (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Actor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secondary Actor</t>
+    <t>Use Case</t>
+  </si>
+  <si>
+    <t>Entity1 (CRUD)</t>
+  </si>
+  <si>
+    <t>Entity2 (CRUD)</t>
+  </si>
+  <si>
+    <t>Primary Actor</t>
+  </si>
+  <si>
+    <t>Secondary Actor</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">View Home Page &amp; Movie Catalog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movie (Read)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genre (Read)</t>
+    <t>View Home Page &amp; Movie Catalog</t>
+  </si>
+  <si>
+    <t>Movie (Read)</t>
+  </si>
+  <si>
+    <t>Genre (Read)</t>
   </si>
   <si>
     <t>Guest</t>
@@ -805,398 +644,405 @@
     <t>None</t>
   </si>
   <si>
-    <t xml:space="preserve">As a guest, I want to view now showing and coming soon movies on the home page so that I can discover movies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Movie Details &amp; Trailer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a guest, I want to view movie synopsis, duration, age rating and watch trailer so that I can choose what to watch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search &amp; Filter Movies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a guest, I want to search movies by title and filter by genre so that I can quickly find my preferred movie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Cinema Branches</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cinema (Read)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a guest, I want to view the list of cinema locations and hotline so that I can choose a cinema near me.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Showtime Schedules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Showtime (Read)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a guest, I want to check movie screening schedules and hall types across dates and branches.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Register Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User (Create)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a guest, I want to register an account with email verification so that I can become a registered customer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User (Read)</t>
+    <t>As a guest, I want to view now showing and coming soon movies on the home page so that I can discover movies.</t>
+  </si>
+  <si>
+    <t>View Movie Details &amp; Trailer</t>
+  </si>
+  <si>
+    <t>As a guest, I want to view movie synopsis, duration, age rating and watch trailer so that I can choose what to watch.</t>
+  </si>
+  <si>
+    <t>Search &amp; Filter Movies</t>
+  </si>
+  <si>
+    <t>As a guest, I want to search movies by title and filter by genre so that I can quickly find my preferred movie.</t>
+  </si>
+  <si>
+    <t>View Cinema Branches</t>
+  </si>
+  <si>
+    <t>Cinema (Read)</t>
+  </si>
+  <si>
+    <t>As a guest, I want to view the list of cinema locations and hotline so that I can choose a cinema near me.</t>
+  </si>
+  <si>
+    <t>View Showtime Schedules</t>
+  </si>
+  <si>
+    <t>Showtime (Read)</t>
+  </si>
+  <si>
+    <t>As a guest, I want to check movie screening schedules and hall types across dates and branches.</t>
+  </si>
+  <si>
+    <t>Register Account</t>
+  </si>
+  <si>
+    <t>User (Create)</t>
+  </si>
+  <si>
+    <t>Email Service</t>
+  </si>
+  <si>
+    <t>As a guest, I want to register an account with email verification so that I can become a registered customer.</t>
+  </si>
+  <si>
+    <t>User (Read)</t>
   </si>
   <si>
     <t>Customer</t>
   </si>
   <si>
-    <t xml:space="preserve">As a registered customer, I want to log in with email and password so that I can access personalized features.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a logged-in user, I want to log out to terminate my active session.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reset Forgotten Password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User (Update)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a customer, I want to receive a 15-minute password reset token via email so that I can recover my account.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Customer Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User (Read, Update)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a customer, I want to view and update my phone number, full name, and avatar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a customer, I want to update my account password to maintain security.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select Seats &amp; Hold 5 Minutes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SeatHolding (Create)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seat (Read)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Lock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a customer, I want to select seats on the visual room map and hold them for 5 minutes during checkout.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select F&amp;B Combos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FnBItem (Read)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OrderItem (Create)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a customer, I want to add popcorn and beverage combos to my booking order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay Booking via VNPay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment (Create)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Booking (Update)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VNPay Gateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a customer, I want to complete payment online via VNPay gateway to confirm ticket purchase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Booking History &amp; E-Ticket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Booking (Read)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ticket (Read)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a customer, I want to access my booking history and view digital QR tickets for cinema entry.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit Movie Rating &amp; Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review (Create, Update)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a customer, I want to rate 1-5 stars and write a movie review after watching.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sell Tickets at Counter (POS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Booking (Create)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ticket (Create)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cinema Staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Staff, I want to select showtimes, seats, and create booking orders for walk-in counter customers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order F&amp;B at Counter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Staff, I want to add food and drink items to customer orders at the POS counter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Process Cash / Card Payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Staff, I want to collect cash or card payment and print receipt at counter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Print Ticket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thermal Printer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Staff, I want to print physical ticket paper with barcodes for counter customers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan QR Ticket at Gate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ticket (Read, Update)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TicketCheckinLog (Create)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QR Camera Scanner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Staff, I want to scan QR code on customer e-tickets to validate entry into cinema halls.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify Customer Age (T13/T16/T18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Staff, I want to check customer identity card against movie age restriction ratings.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Look Up &amp; Reprint Ticket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Staff, I want to look up tickets by booking code or customer phone number to reissue lost tickets.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Shift Cash Drawer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CashDrawer (Create, Update)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Staff, I want to open shift with starting cash balance and close shift with ending cash count.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Personal Shift Report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CashDrawer (Read)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment (Read)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Staff, I want to view my individual shift cash sales summary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schedule Branch Showtimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Showtime (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScreeningRoom (Read)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cinema Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Buffer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Manager, I want to schedule showtimes with automatic 15-minute room cleaning buffer validation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configure Branch Pricing Overrides</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TicketPricing (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Manager, I want to override ticket pricing rules for specific local branch requirements.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitor Hall Occupancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Manager, I want to view real-time seat occupancy and booking status across halls.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Branch F&amp;B Stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CinemaInventory (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Manager, I want to track and update concession inventory levels at my branch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toggle Seat Maintenance Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seat (Update)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaintenanceSchedule (Create)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Manager, I want to set damaged seats under maintenance to prevent customer booking.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View Branch Revenue &amp; Sales Reports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Cinema Manager, I want to inspect sales and revenue reports for my branch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage User, Staff &amp; Manager Accounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role (Read)</t>
+    <t>As a registered customer, I want to log in with email and password so that I can access personalized features.</t>
+  </si>
+  <si>
+    <t>As a logged-in user, I want to log out to terminate my active session.</t>
+  </si>
+  <si>
+    <t>Reset Forgotten Password</t>
+  </si>
+  <si>
+    <t>User (Update)</t>
+  </si>
+  <si>
+    <t>As a customer, I want to receive a 15-minute password reset token via email so that I can recover my account.</t>
+  </si>
+  <si>
+    <t>Manage Customer Profile</t>
+  </si>
+  <si>
+    <t>User (Read, Update)</t>
+  </si>
+  <si>
+    <t>As a customer, I want to view and update my phone number, full name, and avatar.</t>
+  </si>
+  <si>
+    <t>As a customer, I want to update my account password to maintain security.</t>
+  </si>
+  <si>
+    <t>Select Seats &amp; Hold 5 Minutes</t>
+  </si>
+  <si>
+    <t>SeatHolding (Create)</t>
+  </si>
+  <si>
+    <t>Seat (Read)</t>
+  </si>
+  <si>
+    <t>System Lock</t>
+  </si>
+  <si>
+    <t>As a customer, I want to select seats on the visual room map and hold them for 5 minutes during checkout.</t>
+  </si>
+  <si>
+    <t>Select F&amp;B Combos</t>
+  </si>
+  <si>
+    <t>FnBItem (Read)</t>
+  </si>
+  <si>
+    <t>OrderItem (Create)</t>
+  </si>
+  <si>
+    <t>As a customer, I want to add popcorn and beverage combos to my booking order.</t>
+  </si>
+  <si>
+    <t>Pay Booking via VNPay</t>
+  </si>
+  <si>
+    <t>Payment (Create)</t>
+  </si>
+  <si>
+    <t>Booking (Update)</t>
+  </si>
+  <si>
+    <t>VNPay Gateway</t>
+  </si>
+  <si>
+    <t>As a customer, I want to complete payment online via VNPay gateway to confirm ticket purchase.</t>
+  </si>
+  <si>
+    <t>View Booking History &amp; E-Ticket</t>
+  </si>
+  <si>
+    <t>Booking (Read)</t>
+  </si>
+  <si>
+    <t>Ticket (Read)</t>
+  </si>
+  <si>
+    <t>As a customer, I want to access my booking history and view digital QR tickets for cinema entry.</t>
+  </si>
+  <si>
+    <t>Cancel Booking (Conditional)</t>
+  </si>
+  <si>
+    <t>Ticket (Update)</t>
+  </si>
+  <si>
+    <t>System / VNPay Refund</t>
+  </si>
+  <si>
+    <t>As a customer, I want to cancel my paid booking at least X hours prior to screening to receive an automated refund and release reserved seats.</t>
+  </si>
+  <si>
+    <t>Submit Movie Rating &amp; Review</t>
+  </si>
+  <si>
+    <t>Review (Create, Update)</t>
+  </si>
+  <si>
+    <t>As a customer, I want to rate 1-5 stars and write a movie review after watching.</t>
+  </si>
+  <si>
+    <t>Sell Tickets at Counter</t>
+  </si>
+  <si>
+    <t>Booking (Create)</t>
+  </si>
+  <si>
+    <t>Ticket (Create)</t>
+  </si>
+  <si>
+    <t>Cinema Staff</t>
+  </si>
+  <si>
+    <t>As Cinema Staff, I want to select showtimes, seats, select concession ticket types (Standard/Student/Senior) upon ID verification, and create booking orders at counter.</t>
+  </si>
+  <si>
+    <t>Order F&amp;B at Counter</t>
+  </si>
+  <si>
+    <t>As Cinema Staff, I want to browse menu with real-time stock check, and add food &amp; drink items to customer orders at the POS counter.</t>
+  </si>
+  <si>
+    <t>Process Counter Payment</t>
+  </si>
+  <si>
+    <t>As Cinema Staff, I want to collect cash or VNPay payment recorded with staff_id and print receipt at counter.</t>
+  </si>
+  <si>
+    <t>Print Ticket</t>
+  </si>
+  <si>
+    <t>Thermal Printer</t>
+  </si>
+  <si>
+    <t>As Cinema Staff, I want to print physical ticket paper with barcodes for counter customers.</t>
+  </si>
+  <si>
+    <t>Validate QR Ticket</t>
+  </si>
+  <si>
+    <t>Ticket (Read, Update)</t>
+  </si>
+  <si>
+    <t>TicketCheckinLog (Create)</t>
+  </si>
+  <si>
+    <t>QR Camera Scanner</t>
+  </si>
+  <si>
+    <t>As Cinema Staff, I want to scan QR code on customer e-tickets to validate entry, verify showtime &amp; hall, and prevent duplicate entry.</t>
+  </si>
+  <si>
+    <t>Verify Age &amp; Concession Eligibility</t>
+  </si>
+  <si>
+    <t>As Cinema Staff, I want to check customer identity card against movie age restriction ratings (T13/T16/T18) and student card for concession tickets.</t>
+  </si>
+  <si>
+    <t>Reissue / Cancel Ticket</t>
+  </si>
+  <si>
+    <t>As Cinema Staff, I want to cancel tickets with authorized rollback or reissue tickets for customers.</t>
+  </si>
+  <si>
+    <t>Look Up &amp; Reprint Ticket</t>
+  </si>
+  <si>
+    <t>As Cinema Staff, I want to look up tickets by booking code or customer phone number to reissue lost tickets.</t>
+  </si>
+  <si>
+    <t>Schedule Branch Showtimes</t>
+  </si>
+  <si>
+    <t>Showtime (CRUD)</t>
+  </si>
+  <si>
+    <t>ScreeningRoom (Read)</t>
+  </si>
+  <si>
+    <t>Cinema Manager</t>
+  </si>
+  <si>
+    <t>System Buffer</t>
+  </si>
+  <si>
+    <t>As Cinema Manager, I want to schedule showtimes with automatic 15-minute room cleaning buffer validation.</t>
+  </si>
+  <si>
+    <t>Configure Branch Pricing &amp; Rates</t>
+  </si>
+  <si>
+    <t>TicketPricing (CRUD)</t>
+  </si>
+  <si>
+    <t>As Cinema Manager, I want to configure and override ticket pricing rules for specific local branch requirements.</t>
+  </si>
+  <si>
+    <t>Monitor Hall Occupancy</t>
+  </si>
+  <si>
+    <t>As Cinema Manager, I want to view real-time seat occupancy and booking status across halls.</t>
+  </si>
+  <si>
+    <t>Manage Branch F&amp;B Stock</t>
+  </si>
+  <si>
+    <t>CinemaInventory (CRUD)</t>
+  </si>
+  <si>
+    <t>As Cinema Manager, I want to inspect and update concession inventory levels per branch with automated out-of-stock guards.</t>
+  </si>
+  <si>
+    <t>Toggle Seat Maintenance Status</t>
+  </si>
+  <si>
+    <t>Seat (Update)</t>
+  </si>
+  <si>
+    <t>MaintenanceSchedule (Create)</t>
+  </si>
+  <si>
+    <t>As Cinema Manager, I want to set damaged seats under maintenance to prevent customer booking.</t>
+  </si>
+  <si>
+    <t>View Branch Revenue &amp; Sales Reports</t>
+  </si>
+  <si>
+    <t>Payment (Read)</t>
+  </si>
+  <si>
+    <t>As Cinema Manager, I want to inspect sales and revenue reports for my branch.</t>
+  </si>
+  <si>
+    <t>Manage User, Staff &amp; Manager Accounts</t>
+  </si>
+  <si>
+    <t>User (CRUD)</t>
+  </si>
+  <si>
+    <t>Role (Read)</t>
   </si>
   <si>
     <t>Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">As an Administrator, I want to create, update, deactivate staff accounts and assign them to branches.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Master Movie Catalog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movie (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genre (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As an Administrator, I want to add, edit, or archive movies and configure genres and age ratings.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Cinema Branches &amp; Rooms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cinema (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScreeningRoom (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As an Administrator, I want to manage branches, screening halls, and hall formats.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configure Seat Grid Designer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seat (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SeatType (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As an Administrator, I want to configure the physical seat matrix and layout per hall.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configure Global Pricing Templates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As an Administrator, I want to configure chain-wide default pricing by hall format and time slot.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manage Global F&amp;B Catalog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FnBItem (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FnBCategory (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As an Administrator, I want to manage master food and drink items, categories, and standard retail prices.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moderate User Reviews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As an Administrator, I want to approve or hide customer reviews containing inappropriate content.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate Enterprise BI Reports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As an Administrator, I want to view chain-wide financial performance, branch comparisons, and export Excel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Dashboard &amp; Global Parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SystemSetting (CRUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As an Administrator, I want to configure system parameters like hold duration and point accumulation ratio.</t>
+    <t>As an Administrator, I want to create, update, deactivate staff accounts and assign them to branches.</t>
+  </si>
+  <si>
+    <t>Manage Master Movie Catalog</t>
+  </si>
+  <si>
+    <t>Movie (CRUD)</t>
+  </si>
+  <si>
+    <t>Genre (CRUD)</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to add, edit, or archive movies and configure genres and age ratings.</t>
+  </si>
+  <si>
+    <t>Manage Cinema Branches &amp; Halls</t>
+  </si>
+  <si>
+    <t>Cinema (CRUD)</t>
+  </si>
+  <si>
+    <t>ScreeningRoom (CRUD)</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to add, edit, or archive cinema branches, screening halls, and configure hall formats.</t>
+  </si>
+  <si>
+    <t>Configure Seat Grid Designer</t>
+  </si>
+  <si>
+    <t>Seat (CRUD)</t>
+  </si>
+  <si>
+    <t>SeatType (CRUD)</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to configure the physical seat matrix and layout per hall.</t>
+  </si>
+  <si>
+    <t>Configure Default Pricing Template</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to configure chain-wide default pricing by hall format, seat type, time slot, and concession customer types.</t>
+  </si>
+  <si>
+    <t>Manage Global F&amp;B Catalog</t>
+  </si>
+  <si>
+    <t>FnBItem (CRUD)</t>
+  </si>
+  <si>
+    <t>FnBCategory (CRUD)</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to manage master food and drink items, categories, and standard retail prices.</t>
+  </si>
+  <si>
+    <t>Moderate User Reviews</t>
+  </si>
+  <si>
+    <t>Review (CRUD)</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to approve or hide customer reviews containing inappropriate content.</t>
+  </si>
+  <si>
+    <t>Generate Enterprise BI Reports</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to view chain-wide financial performance, branch comparisons, and export Excel.</t>
+  </si>
+  <si>
+    <t>System Dashboard &amp; Global Parameters</t>
+  </si>
+  <si>
+    <t>SystemSetting (CRUD)</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to configure system parameters like hold duration and point accumulation ratio.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.000000"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
+      <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1213,7 +1059,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -1221,37 +1081,20 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
     </xf>
-    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1262,6 +1105,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1746,23 +1592,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O44"/>
+  <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26"/>
-    <col customWidth="1" min="2" max="2" width="14"/>
-    <col customWidth="1" min="3" max="6" width="18"/>
-    <col customWidth="1" min="7" max="7" width="28"/>
-    <col customWidth="1" min="8" max="8" width="55"/>
-    <col customWidth="1" min="9" max="9" width="12"/>
-    <col customWidth="1" min="10" max="10" width="14"/>
-    <col customWidth="1" min="11" max="11" width="12"/>
-    <col customWidth="1" min="12" max="12" width="25"/>
-    <col customWidth="1" min="13" max="13" width="14"/>
-    <col customWidth="1" min="14" max="14" width="45"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="55" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="25" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
+    <row r="1" ht="14.25" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1807,7 +1654,7 @@
       </c>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" ht="28.5">
+    <row r="2" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1839,15 +1686,14 @@
         <v>22</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N2" s="3"/>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" ht="42.75">
+    <row r="3" ht="42.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>15</v>
@@ -1862,13 +1708,13 @@
         <v>17</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>21</v>
@@ -1877,21 +1723,20 @@
         <v>22</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="3">
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N3" s="3"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" ht="28.5">
+    <row r="4" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>16</v>
@@ -1899,10 +1744,10 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>19</v>
@@ -1911,27 +1756,26 @@
         <v>20</v>
       </c>
       <c r="K4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="3"/>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4" s="3">
-      </c>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" ht="28.5">
-      <c r="A5" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>16</v>
@@ -1939,115 +1783,112 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5" s="3">
-      </c>
+      <c r="N5" s="3"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" ht="42.75">
+    <row r="6" ht="42.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N6" s="3">
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N6" s="3"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" ht="28.5">
+    <row r="7" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7" s="3">
-      </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" ht="28.5">
-      <c r="A8" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>15</v>
@@ -2056,17 +1897,17 @@
         <v>16</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>19</v>
@@ -2075,2418 +1916,2297 @@
         <v>20</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N8" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N8" s="3"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" ht="28.5">
+    <row r="9" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" s="3">
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N9" s="3"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" ht="28.5">
+    <row r="10" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10" s="3">
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N10" s="3"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" ht="28.5">
+    <row r="11" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" s="3">
-      </c>
+      <c r="N11" s="3"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" ht="28.5">
+    <row r="12" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N12" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N12" s="3"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" ht="28.5">
+    <row r="13" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N13" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N13" s="3"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" ht="28.5">
+    <row r="14" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N14" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N14" s="3"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" ht="28.5">
+    <row r="15" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="I15" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N15" s="3">
-      </c>
+      <c r="N15" s="3"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" ht="28.5">
+    <row r="16" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N16" s="3">
-      </c>
+      <c r="N16" s="3"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" ht="28.5">
+    <row r="17" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N17" s="3">
-      </c>
+      <c r="N17" s="3"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" ht="28.5">
+    <row r="18" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N18" s="3">
-      </c>
+      <c r="N18" s="3"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" ht="42.75">
+    <row r="19" ht="42.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N19" s="3">
-      </c>
+      <c r="N19" s="3"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" ht="42.75">
+    <row r="20" ht="42.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N20" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N20" s="3"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" ht="28.5">
+    <row r="21" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N21" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N21" s="3"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" ht="28.5">
+    <row r="22" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N22" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N22" s="3"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" ht="28.5">
+    <row r="23" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N23" s="3">
-      </c>
+      <c r="N23" s="3"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" ht="28.5">
+    <row r="24" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N24" s="3">
-      </c>
+      <c r="N24" s="3"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" ht="28.5">
+    <row r="25" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N25" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N25" s="3"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" ht="42.75">
+    <row r="26" ht="42.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" ht="42.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N26" s="3">
-      </c>
-      <c r="O26" s="2"/>
-    </row>
-    <row r="27" ht="42.75">
-      <c r="A27" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N27" s="3">
-      </c>
+      <c r="N27" s="3"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" ht="28.5">
+    <row r="28" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N28" s="3">
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N28" s="3"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" ht="28.5">
+    <row r="29" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N29" s="3">
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N29" s="3"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" ht="28.5">
+    <row r="30" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N30" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N30" s="3"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" ht="28.5">
+    <row r="31" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N31" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N31" s="3"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" ht="71.25">
+    <row r="32" ht="71.25" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="J32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M32" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N32" s="3">
-      </c>
+      <c r="N32" s="3"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" ht="28.5">
+    <row r="33" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N33" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N33" s="3"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" ht="28.5">
+    <row r="34" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="J34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="M34" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K34" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N34" s="3">
-      </c>
+      <c r="N34" s="3"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" ht="28.5">
+    <row r="35" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="J35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="M35" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N35" s="3">
-      </c>
+      <c r="N35" s="3"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" ht="28.5">
+    <row r="36" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="J36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="M36" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K36" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N36" s="3">
-      </c>
+      <c r="N36" s="3"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" ht="28.5">
+    <row r="37" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="G37" s="3" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N37" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N37" s="3"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" ht="28.5">
+    <row r="38" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N38" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N38" s="3"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" ht="28.5">
+    <row r="39" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N39" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N39" s="3"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" ht="28.5">
+    <row r="40" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="J40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="M40" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N40" s="3">
-      </c>
+      <c r="N40" s="3"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" ht="28.5">
+    <row r="41" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N41" s="3">
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N41" s="3"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" ht="28.5">
+    <row r="42" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>231</v>
+        <v>190</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N42" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N42" s="3"/>
       <c r="O42" s="2"/>
     </row>
-    <row r="43" ht="28.5">
+    <row r="43" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N43" s="3">
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N43" s="3"/>
       <c r="O43" s="2"/>
     </row>
-    <row r="44" ht="28.5">
+    <row r="44" ht="28.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>197</v>
+        <v>162</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N44" s="3">
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N44" s="3"/>
       <c r="O44" s="2"/>
     </row>
-    <row r="45" ht="42.75">
-      <c r="A45" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N45" s="3">
-      </c>
-      <c r="O45" s="2"/>
-    </row>
-    <row r="46" ht="28.5">
-      <c r="A46" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N46" s="3">
-      </c>
-      <c r="O46" s="2"/>
-    </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter>
-  </headerFooter>
+  <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="35"/>
-    <col customWidth="1" min="2" max="3" width="22"/>
-    <col customWidth="1" min="4" max="5" width="18"/>
-    <col customWidth="1" min="6" max="6" width="65"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="G1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>261</v>
+        <v>208</v>
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="G3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>265</v>
+        <v>212</v>
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>266</v>
+        <v>213</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>267</v>
+        <v>214</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="G5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="G6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>274</v>
+        <v>221</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="G7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>276</v>
+        <v>223</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="G8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>276</v>
+        <v>223</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>274</v>
+        <v>221</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>282</v>
+        <v>229</v>
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>283</v>
+        <v>230</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>285</v>
+        <v>232</v>
       </c>
       <c r="G11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>343</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>339</v>
+        <v>285</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>344</v>
+        <v>290</v>
       </c>
       <c r="G28" s="2"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="s">
-        <v>356</v>
-      </c>
       <c r="B33" s="3" t="s">
-        <v>357</v>
+        <v>304</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>358</v>
+        <v>305</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>360</v>
+        <v>307</v>
       </c>
       <c r="G33" s="2"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>361</v>
+        <v>308</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>362</v>
+        <v>309</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>363</v>
+        <v>310</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>364</v>
+        <v>311</v>
       </c>
       <c r="G34" s="2"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>365</v>
+        <v>312</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>366</v>
+        <v>313</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>367</v>
+        <v>314</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>368</v>
+        <v>315</v>
       </c>
       <c r="G35" s="2"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>369</v>
+        <v>316</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>370</v>
+        <v>317</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G36" s="2"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>343</v>
+        <v>289</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>374</v>
+        <v>321</v>
       </c>
       <c r="G37" s="2"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>375</v>
+        <v>322</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>376</v>
+        <v>323</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>377</v>
+        <v>324</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="G38" s="2"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>379</v>
+        <v>326</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>381</v>
+        <v>328</v>
       </c>
       <c r="G39" s="2"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>383</v>
+        <v>330</v>
       </c>
       <c r="G40" s="2"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>384</v>
+        <v>331</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>385</v>
+        <v>332</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>386</v>
+        <v>333</v>
       </c>
       <c r="G41" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>